--- a/PartsListJPN_230331.xlsx
+++ b/PartsListJPN_230331.xlsx
@@ -1,36 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Box\Anis Laboratory\Homepage\operanthouse\HTML\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C4F32F-02FA-48D8-9B26-12CDC456287D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="1630" windowWidth="21980" windowHeight="18840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="135" yWindow="15" windowWidth="26265" windowHeight="18705" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="PartList" sheetId="1" r:id="rId1"/>
     <sheet name="OptionParts" sheetId="3" r:id="rId2"/>
     <sheet name="Note" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="145621" concurrentCalc="0"/>
 </workbook>
 </file>
 
@@ -1170,6 +1151,9 @@
     <t>NNAMC3460PCEV</t>
   </si>
   <si>
+    <t>Alternative of Airbar</t>
+  </si>
+  <si>
     <t>Digi-Key</t>
   </si>
   <si>
@@ -1193,19 +1177,16 @@
   <si>
     <t>USB cable (Type A to microB, 0.3m)</t>
     <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Alternative of Airbar, Touch area:(345.6x208.5mm)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_);[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1288,7 +1269,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1340,7 +1321,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1350,7 +1331,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1362,7 +1346,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1374,19 +1361,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1401,17 +1397,32 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="ハイパーリンク" xfId="2" builtinId="8"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準 2" xfId="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1419,17 +1430,14 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office ​​テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1467,7 +1475,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1539,7 +1547,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1712,25 +1720,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M59"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.58203125" style="6" customWidth="1"/>
-    <col min="2" max="2" width="36.25" customWidth="1"/>
-    <col min="3" max="3" width="56.9140625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="43.08203125" customWidth="1"/>
-    <col min="5" max="5" width="26.4140625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" style="8" customWidth="1"/>
-    <col min="7" max="7" width="7.9140625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="41.5546875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="36.21875" customWidth="1"/>
+    <col min="3" max="3" width="56.88671875" style="10" customWidth="1"/>
+    <col min="4" max="4" width="43.109375" customWidth="1"/>
+    <col min="5" max="5" width="26.44140625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" style="10" customWidth="1"/>
+    <col min="7" max="7" width="7.88671875" style="16" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" style="17" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="7.9140625" style="8" customWidth="1"/>
-    <col min="14" max="16384" width="8.75" style="8"/>
+    <col min="11" max="12" width="7.88671875" style="10" customWidth="1"/>
+    <col min="14" max="16384" width="8.77734375" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="5" customFormat="1" ht="48" customHeight="1">
+    <row r="1" spans="1:13" s="6" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1747,1593 +1755,1595 @@
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13">
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9">
         <f>SUM(J3:J143)</f>
         <v>55903.740000000005</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4" spans="1:13" s="12" customFormat="1">
-      <c r="A4" s="6"/>
-      <c r="B4" s="9" t="s">
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+    </row>
+    <row r="4" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="10">
-        <v>1</v>
-      </c>
-      <c r="H4" s="10">
-        <v>1</v>
-      </c>
-      <c r="I4" s="11">
+      <c r="G4" s="13">
+        <v>1</v>
+      </c>
+      <c r="H4" s="13">
+        <v>1</v>
+      </c>
+      <c r="I4" s="14">
         <v>9800</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="12">
         <f>H4*I4</f>
         <v>9800</v>
       </c>
-      <c r="K4" s="10"/>
-      <c r="L4" s="4" t="s">
+      <c r="K4" s="12"/>
+      <c r="L4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="10"/>
-    </row>
-    <row r="5" spans="1:13" s="12" customFormat="1">
-      <c r="B5" s="10"/>
-      <c r="C5" s="10" t="s">
+      <c r="M4" s="12"/>
+    </row>
+    <row r="5" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="12"/>
+      <c r="C5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="10">
-        <v>1</v>
-      </c>
-      <c r="H5" s="10">
-        <v>1</v>
-      </c>
-      <c r="I5" s="11">
+      <c r="G5" s="13">
+        <v>1</v>
+      </c>
+      <c r="H5" s="13">
+        <v>1</v>
+      </c>
+      <c r="I5" s="14">
         <v>1780</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="12">
         <f>H5*I5</f>
         <v>1780</v>
       </c>
-      <c r="K5" s="10"/>
-      <c r="L5" s="4" t="s">
+      <c r="K5" s="12"/>
+      <c r="L5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="M5" s="10"/>
-    </row>
-    <row r="6" spans="1:13" s="12" customFormat="1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10" t="s">
+      <c r="M5" s="12"/>
+    </row>
+    <row r="6" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="10">
-        <v>1</v>
-      </c>
-      <c r="H6" s="10">
-        <v>1</v>
-      </c>
-      <c r="I6" s="11">
+      <c r="G6" s="13">
+        <v>1</v>
+      </c>
+      <c r="H6" s="13">
+        <v>1</v>
+      </c>
+      <c r="I6" s="14">
         <v>6898</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="12">
         <f>H6*I6</f>
         <v>6898</v>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="4" t="s">
+      <c r="K6" s="12"/>
+      <c r="L6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M6" s="10"/>
-    </row>
-    <row r="7" spans="1:13" s="12" customFormat="1">
-      <c r="A7" s="6"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="10"/>
-    </row>
-    <row r="8" spans="1:13" s="12" customFormat="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10" t="s">
+      <c r="M6" s="12"/>
+    </row>
+    <row r="7" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="12"/>
+    </row>
+    <row r="8" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="10">
-        <v>1</v>
-      </c>
-      <c r="H8" s="10">
-        <v>1</v>
-      </c>
-      <c r="I8" s="11">
+      <c r="G8" s="13">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13">
+        <v>1</v>
+      </c>
+      <c r="I8" s="14">
         <v>2930</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="12">
         <f>H8*I8</f>
         <v>2930</v>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="4" t="s">
+      <c r="K8" s="12"/>
+      <c r="L8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="M8" s="10"/>
-    </row>
-    <row r="9" spans="1:13" s="12" customFormat="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10" t="s">
+      <c r="M8" s="12"/>
+    </row>
+    <row r="9" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="10">
-        <v>1</v>
-      </c>
-      <c r="H9" s="10">
-        <v>1</v>
-      </c>
-      <c r="I9" s="11">
+      <c r="G9" s="13">
+        <v>1</v>
+      </c>
+      <c r="H9" s="13">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14">
         <v>321</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="12">
         <f>H9*I9</f>
         <v>321</v>
       </c>
-      <c r="K9" s="10"/>
-      <c r="L9" s="4" t="s">
+      <c r="K9" s="12"/>
+      <c r="L9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="M9" s="10"/>
-    </row>
-    <row r="10" spans="1:13" s="12" customFormat="1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="10"/>
-    </row>
-    <row r="11" spans="1:13" s="12" customFormat="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="9" t="s">
+      <c r="M9" s="12"/>
+    </row>
+    <row r="10" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="12"/>
+    </row>
+    <row r="11" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="10">
-        <v>1</v>
-      </c>
-      <c r="H11" s="10">
+      <c r="G11" s="13">
+        <v>1</v>
+      </c>
+      <c r="H11" s="13">
         <v>2</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="14">
         <v>9777</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="12">
         <f>H11*I11</f>
         <v>19554</v>
       </c>
-      <c r="K11" s="10"/>
-      <c r="L11" s="4" t="s">
+      <c r="K11" s="12"/>
+      <c r="L11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="M11" s="10"/>
-    </row>
-    <row r="12" spans="1:13" s="12" customFormat="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10" t="s">
+      <c r="M11" s="12"/>
+    </row>
+    <row r="12" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="10">
-        <v>1</v>
-      </c>
-      <c r="H12" s="10">
+      <c r="G12" s="13">
+        <v>1</v>
+      </c>
+      <c r="H12" s="13">
         <v>2</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="14">
         <v>786</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="12">
         <f>H12*I12</f>
         <v>1572</v>
       </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="4" t="s">
+      <c r="K12" s="12"/>
+      <c r="L12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="M12" s="10"/>
-    </row>
-    <row r="13" spans="1:13" s="12" customFormat="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="9" t="s">
+      <c r="M12" s="12"/>
+    </row>
+    <row r="13" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="10">
-        <v>1</v>
-      </c>
-      <c r="H13" s="10">
-        <v>1</v>
-      </c>
-      <c r="I13" s="11">
+      <c r="G13" s="13">
+        <v>1</v>
+      </c>
+      <c r="H13" s="13">
+        <v>1</v>
+      </c>
+      <c r="I13" s="14">
         <v>5499</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="12">
         <f>H13*I13</f>
         <v>5499</v>
       </c>
-      <c r="K13" s="10"/>
-      <c r="L13" s="4" t="s">
+      <c r="K13" s="12"/>
+      <c r="L13" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="M13" s="10"/>
-    </row>
-    <row r="14" spans="1:13" s="12" customFormat="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="10"/>
-    </row>
-    <row r="15" spans="1:13" s="12" customFormat="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="10"/>
-    </row>
-    <row r="16" spans="1:13" s="12" customFormat="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="11"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="10"/>
-    </row>
-    <row r="17" spans="1:13" s="12" customFormat="1">
-      <c r="A17" s="6"/>
-      <c r="B17" s="9" t="s">
+      <c r="M13" s="12"/>
+    </row>
+    <row r="14" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="12"/>
+    </row>
+    <row r="15" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="12"/>
+    </row>
+    <row r="16" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="12"/>
+    </row>
+    <row r="17" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="10">
-        <v>1</v>
-      </c>
-      <c r="H17" s="10">
-        <v>1</v>
-      </c>
-      <c r="I17" s="11">
+      <c r="G17" s="13">
+        <v>1</v>
+      </c>
+      <c r="H17" s="13">
+        <v>1</v>
+      </c>
+      <c r="I17" s="14">
         <v>90</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="12">
         <f t="shared" ref="J17:J22" si="0">H17*I17</f>
         <v>90</v>
       </c>
-      <c r="K17" s="10"/>
-      <c r="L17" s="4" t="s">
+      <c r="K17" s="12"/>
+      <c r="L17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="M17" s="10"/>
-    </row>
-    <row r="18" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B18" s="10"/>
-      <c r="C18" s="10" t="s">
+      <c r="M17" s="12"/>
+    </row>
+    <row r="18" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="12"/>
+      <c r="C18" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G18" s="10">
-        <v>1</v>
-      </c>
-      <c r="H18" s="10">
-        <v>1</v>
-      </c>
-      <c r="I18" s="11">
+      <c r="G18" s="13">
+        <v>1</v>
+      </c>
+      <c r="H18" s="13">
+        <v>1</v>
+      </c>
+      <c r="I18" s="14">
         <v>1000</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="12">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="4" t="s">
+      <c r="K18" s="12"/>
+      <c r="L18" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="M18" s="10"/>
-    </row>
-    <row r="19" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B19" s="10"/>
-      <c r="C19" s="10" t="s">
+      <c r="M18" s="12"/>
+    </row>
+    <row r="19" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="12"/>
+      <c r="C19" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="13">
         <v>100</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="13">
         <v>0.04</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="14">
         <v>100</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="12">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K19" s="10"/>
-      <c r="L19" s="4" t="s">
+      <c r="K19" s="12"/>
+      <c r="L19" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="M19" s="10"/>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="B20" s="4"/>
-      <c r="C20" s="10" t="s">
+      <c r="M19" s="12"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B20" s="5"/>
+      <c r="C20" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="13">
         <v>100</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="13">
         <v>0.05</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="14">
         <v>100</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="12">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4" t="s">
+      <c r="K20" s="5"/>
+      <c r="L20" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="M20" s="4"/>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="B21" s="4"/>
-      <c r="C21" s="10" t="s">
+      <c r="M20" s="5"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B21" s="5"/>
+      <c r="C21" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="13">
         <v>100</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="13">
         <v>0.02</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="14">
         <v>100</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="12">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4" t="s">
+      <c r="K21" s="5"/>
+      <c r="L21" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="M21" s="4"/>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="B22" s="4"/>
-      <c r="C22" s="10" t="s">
+      <c r="M21" s="5"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B22" s="5"/>
+      <c r="C22" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="13">
         <v>100</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="13">
         <v>0.02</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="14">
         <v>100</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="12">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4" t="s">
+      <c r="K22" s="5"/>
+      <c r="L22" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="M22" s="4"/>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-    </row>
-    <row r="24" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B24" s="10"/>
-      <c r="C24" s="4" t="s">
+      <c r="M22" s="5"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+    </row>
+    <row r="24" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="12"/>
+      <c r="C24" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G24" s="10">
-        <v>1</v>
-      </c>
-      <c r="H24" s="10">
+      <c r="G24" s="13">
+        <v>1</v>
+      </c>
+      <c r="H24" s="13">
         <v>0.3</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="14">
         <v>40</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="12">
         <f t="shared" ref="J24:J34" si="1">H24*I24</f>
         <v>12</v>
       </c>
-      <c r="K24" s="10"/>
-      <c r="L24" s="4" t="s">
+      <c r="K24" s="12"/>
+      <c r="L24" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="M24" s="10"/>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="C25" s="4" t="s">
+      <c r="M24" s="12"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C25" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E25" s="8" t="s">
+      <c r="E25" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G25" s="8">
-        <v>1</v>
-      </c>
-      <c r="H25" s="10">
+      <c r="G25" s="16">
+        <v>1</v>
+      </c>
+      <c r="H25" s="13">
         <v>0.1</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="17">
         <v>50</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="12">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L25" s="8" t="s">
+      <c r="L25" s="10" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B26" s="10"/>
-      <c r="C26" s="10" t="s">
+    <row r="26" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="12"/>
+      <c r="C26" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="13">
         <v>10</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="13">
         <v>0.3</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I26" s="13">
         <v>290</v>
       </c>
-      <c r="J26" s="10">
+      <c r="J26" s="12">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="K26" s="10"/>
-      <c r="L26" s="4" t="s">
+      <c r="K26" s="12"/>
+      <c r="L26" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="M26" s="10"/>
-    </row>
-    <row r="27" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B27" s="10"/>
-      <c r="C27" s="10" t="s">
+      <c r="M26" s="12"/>
+    </row>
+    <row r="27" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="12"/>
+      <c r="C27" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="13">
         <v>120</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="13">
         <v>0.1</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="13">
         <v>589</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J27" s="12">
         <f t="shared" si="1"/>
         <v>58.900000000000006</v>
       </c>
-      <c r="K27" s="10"/>
-      <c r="L27" s="4" t="s">
+      <c r="K27" s="12"/>
+      <c r="L27" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="M27" s="10"/>
-    </row>
-    <row r="28" spans="1:13" s="12" customFormat="1">
-      <c r="A28" s="6"/>
-      <c r="B28" s="10" t="s">
+      <c r="M27" s="12"/>
+    </row>
+    <row r="28" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7"/>
+      <c r="B28" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G28" s="10">
-        <v>1</v>
-      </c>
-      <c r="H28" s="10">
-        <v>1</v>
-      </c>
-      <c r="I28" s="10">
+      <c r="G28" s="13">
+        <v>1</v>
+      </c>
+      <c r="H28" s="13">
+        <v>1</v>
+      </c>
+      <c r="I28" s="13">
         <v>10</v>
       </c>
-      <c r="J28" s="10">
+      <c r="J28" s="12">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="K28" s="10"/>
-      <c r="L28" s="4" t="s">
+      <c r="K28" s="12"/>
+      <c r="L28" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="M28" s="10"/>
-    </row>
-    <row r="29" spans="1:13">
+      <c r="M28" s="12"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>174</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="12" t="s">
         <v>83</v>
       </c>
       <c r="E29" t="s">
         <v>172</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="F29" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="16">
         <v>10</v>
       </c>
-      <c r="H29" s="10">
-        <v>1</v>
-      </c>
-      <c r="I29" s="13">
+      <c r="H29" s="13">
+        <v>1</v>
+      </c>
+      <c r="I29" s="17">
         <v>25</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J29" s="12">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="L29" s="8" t="s">
+      <c r="L29" s="10" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
-      <c r="B30" s="4"/>
-      <c r="C30" s="10" t="s">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B30" s="5"/>
+      <c r="C30" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G30" s="4">
+      <c r="G30" s="8">
         <v>10</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="13">
         <v>0.5</v>
       </c>
-      <c r="I30" s="7">
+      <c r="I30" s="9">
         <v>250</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J30" s="12">
         <f t="shared" si="1"/>
         <v>125</v>
       </c>
-      <c r="K30" s="4"/>
-      <c r="L30" s="19" t="s">
+      <c r="K30" s="5"/>
+      <c r="L30" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="M30" s="4"/>
-    </row>
-    <row r="31" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B31" s="10"/>
-      <c r="C31" s="10" t="s">
+      <c r="M30" s="5"/>
+    </row>
+    <row r="31" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="12"/>
+      <c r="C31" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="13">
         <v>5</v>
       </c>
-      <c r="H31" s="10">
-        <v>1</v>
-      </c>
-      <c r="I31" s="10">
+      <c r="H31" s="13">
+        <v>1</v>
+      </c>
+      <c r="I31" s="13">
         <v>100</v>
       </c>
-      <c r="J31" s="10">
+      <c r="J31" s="12">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="K31" s="10"/>
-      <c r="L31" s="4" t="s">
+      <c r="K31" s="12"/>
+      <c r="L31" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="M31" s="10"/>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="B32" s="4"/>
-      <c r="C32" s="4" t="s">
+      <c r="M31" s="12"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B32" s="5"/>
+      <c r="C32" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G32" s="4">
+      <c r="G32" s="8">
         <v>4</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="13">
         <v>0.25</v>
       </c>
-      <c r="I32" s="7">
+      <c r="I32" s="9">
         <v>1350</v>
       </c>
-      <c r="J32" s="10">
+      <c r="J32" s="12">
         <f t="shared" si="1"/>
         <v>337.5</v>
       </c>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4" t="s">
+      <c r="K32" s="5"/>
+      <c r="L32" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="M32" s="4"/>
-    </row>
-    <row r="33" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B33" s="10"/>
-      <c r="C33" s="10" t="s">
+      <c r="M32" s="5"/>
+    </row>
+    <row r="33" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="12"/>
+      <c r="C33" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="F33" s="10" t="s">
+      <c r="F33" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G33" s="10">
-        <v>1</v>
-      </c>
-      <c r="H33" s="10">
+      <c r="G33" s="13">
+        <v>1</v>
+      </c>
+      <c r="H33" s="13">
         <v>0.1</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="13">
         <v>600</v>
       </c>
-      <c r="J33" s="10">
+      <c r="J33" s="12">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="K33" s="10"/>
-      <c r="L33" s="4" t="s">
+      <c r="K33" s="12"/>
+      <c r="L33" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="M33" s="10"/>
-    </row>
-    <row r="34" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B34" s="10"/>
-      <c r="C34" s="10" t="s">
+      <c r="M33" s="12"/>
+    </row>
+    <row r="34" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="12"/>
+      <c r="C34" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10" t="s">
+      <c r="E34" s="12"/>
+      <c r="F34" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G34" s="10">
-        <v>1</v>
-      </c>
-      <c r="H34" s="10">
+      <c r="G34" s="13">
+        <v>1</v>
+      </c>
+      <c r="H34" s="13">
         <v>0.1</v>
       </c>
-      <c r="I34" s="10">
+      <c r="I34" s="13">
         <v>600</v>
       </c>
-      <c r="J34" s="10">
+      <c r="J34" s="12">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="K34" s="10"/>
-      <c r="L34" s="4" t="s">
+      <c r="K34" s="12"/>
+      <c r="L34" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="M34" s="10"/>
-    </row>
-    <row r="35" spans="1:13" s="12" customFormat="1">
-      <c r="A35" s="6"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="10"/>
-    </row>
-    <row r="36" spans="1:13" s="12" customFormat="1">
-      <c r="A36" s="6"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="10"/>
-    </row>
-    <row r="37" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B37" s="9" t="s">
+      <c r="M34" s="12"/>
+    </row>
+    <row r="35" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="12"/>
+    </row>
+    <row r="36" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="12"/>
+    </row>
+    <row r="37" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="F37" s="10" t="s">
+      <c r="F37" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G37" s="13">
         <v>2</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H37" s="13">
         <v>0.5</v>
       </c>
-      <c r="I37" s="11">
+      <c r="I37" s="14">
         <v>3628</v>
       </c>
-      <c r="J37" s="10">
+      <c r="J37" s="12">
         <f>H37*I37</f>
         <v>1814</v>
       </c>
-      <c r="K37" s="10"/>
-      <c r="L37" s="4" t="s">
+      <c r="K37" s="12"/>
+      <c r="L37" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="M37" s="10"/>
-    </row>
-    <row r="38" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B38" s="10"/>
-      <c r="C38" s="10" t="s">
+      <c r="M37" s="12"/>
+    </row>
+    <row r="38" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="12"/>
+      <c r="C38" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G38" s="10">
+      <c r="G38" s="13">
         <v>12</v>
       </c>
-      <c r="H38" s="10">
+      <c r="H38" s="13">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="I38" s="11">
+      <c r="I38" s="14">
         <v>1380</v>
       </c>
-      <c r="J38" s="10">
+      <c r="J38" s="12">
         <f>H38*I38</f>
         <v>114.54</v>
       </c>
-      <c r="K38" s="10"/>
-      <c r="L38" s="4" t="s">
+      <c r="K38" s="12"/>
+      <c r="L38" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="M38" s="10"/>
-    </row>
-    <row r="39" spans="1:13" s="12" customFormat="1">
-      <c r="A39" s="6"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="10" t="s">
+      <c r="M38" s="12"/>
+    </row>
+    <row r="39" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7"/>
+      <c r="B39" s="12"/>
+      <c r="C39" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10">
-        <v>1</v>
-      </c>
-      <c r="H39" s="10">
-        <v>1</v>
-      </c>
-      <c r="I39" s="11"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="10"/>
-    </row>
-    <row r="40" spans="1:13" s="12" customFormat="1">
-      <c r="A40" s="6"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="10" t="s">
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="13">
+        <v>1</v>
+      </c>
+      <c r="H39" s="13">
+        <v>1</v>
+      </c>
+      <c r="I39" s="14"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="12"/>
+    </row>
+    <row r="40" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10">
-        <v>1</v>
-      </c>
-      <c r="H40" s="10">
-        <v>1</v>
-      </c>
-      <c r="I40" s="11"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="10"/>
-    </row>
-    <row r="41" spans="1:13" s="12" customFormat="1">
-      <c r="A41" s="6"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="10" t="s">
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="13">
+        <v>1</v>
+      </c>
+      <c r="H40" s="13">
+        <v>1</v>
+      </c>
+      <c r="I40" s="14"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="12"/>
+    </row>
+    <row r="41" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="G41" s="10">
-        <v>1</v>
-      </c>
-      <c r="H41" s="10">
-        <v>1</v>
-      </c>
-      <c r="I41" s="10">
+      <c r="G41" s="13">
+        <v>1</v>
+      </c>
+      <c r="H41" s="13">
+        <v>1</v>
+      </c>
+      <c r="I41" s="13">
         <v>475</v>
       </c>
-      <c r="J41" s="10">
+      <c r="J41" s="12">
         <f>H41*I41</f>
         <v>475</v>
       </c>
-      <c r="K41" s="10"/>
-      <c r="L41" s="4" t="s">
+      <c r="K41" s="12"/>
+      <c r="L41" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="M41" s="10"/>
-    </row>
-    <row r="42" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B42" s="10"/>
-      <c r="C42" s="10" t="s">
+      <c r="M41" s="12"/>
+    </row>
+    <row r="42" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="12"/>
+      <c r="C42" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G42" s="10">
-        <v>1</v>
-      </c>
-      <c r="H42" s="10">
+      <c r="G42" s="13">
+        <v>1</v>
+      </c>
+      <c r="H42" s="13">
         <v>1.5</v>
       </c>
-      <c r="I42" s="10">
+      <c r="I42" s="13">
         <v>253</v>
       </c>
-      <c r="J42" s="10">
+      <c r="J42" s="12">
         <f>H42*I42</f>
         <v>379.5</v>
       </c>
-      <c r="K42" s="10"/>
-      <c r="L42" s="4" t="s">
+      <c r="K42" s="12"/>
+      <c r="L42" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="M42" s="10"/>
-    </row>
-    <row r="43" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B43" s="10"/>
-      <c r="C43" s="10" t="s">
+      <c r="M42" s="12"/>
+    </row>
+    <row r="43" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="12"/>
+      <c r="C43" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="F43" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G43" s="10">
-        <v>1</v>
-      </c>
-      <c r="H43" s="10">
-        <v>1</v>
-      </c>
-      <c r="I43" s="11">
+      <c r="G43" s="13">
+        <v>1</v>
+      </c>
+      <c r="H43" s="13">
+        <v>1</v>
+      </c>
+      <c r="I43" s="14">
         <v>973</v>
       </c>
-      <c r="J43" s="10">
+      <c r="J43" s="12">
         <f>H43*I43</f>
         <v>973</v>
       </c>
-      <c r="K43" s="10"/>
-      <c r="L43" s="4" t="s">
+      <c r="K43" s="12"/>
+      <c r="L43" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="M43" s="10"/>
-    </row>
-    <row r="44" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="10"/>
-    </row>
-    <row r="45" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B45" s="9" t="s">
+      <c r="M43" s="12"/>
+    </row>
+    <row r="44" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="13"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="12"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="12"/>
+    </row>
+    <row r="45" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10" t="s">
+      <c r="E45" s="12"/>
+      <c r="F45" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G45" s="10">
+      <c r="G45" s="13">
         <v>20</v>
       </c>
-      <c r="H45" s="10">
-        <v>1</v>
-      </c>
-      <c r="I45" s="11">
+      <c r="H45" s="13">
+        <v>1</v>
+      </c>
+      <c r="I45" s="14">
         <v>6</v>
       </c>
-      <c r="J45" s="10">
+      <c r="J45" s="12">
         <f>H45*I45</f>
         <v>6</v>
       </c>
-      <c r="K45" s="10"/>
-      <c r="L45" s="4" t="s">
+      <c r="K45" s="12"/>
+      <c r="L45" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="M45" s="10"/>
-    </row>
-    <row r="46" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B46" s="10"/>
-      <c r="C46" s="10" t="s">
+      <c r="M45" s="12"/>
+    </row>
+    <row r="46" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="12"/>
+      <c r="C46" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10" t="s">
+      <c r="E46" s="12"/>
+      <c r="F46" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G46" s="10">
+      <c r="G46" s="13">
         <v>10</v>
       </c>
-      <c r="H46" s="10">
-        <v>1</v>
-      </c>
-      <c r="I46" s="11">
+      <c r="H46" s="13">
+        <v>1</v>
+      </c>
+      <c r="I46" s="14">
         <v>13</v>
       </c>
-      <c r="J46" s="10">
+      <c r="J46" s="12">
         <f>H46*I46</f>
         <v>13</v>
       </c>
-      <c r="K46" s="10"/>
-      <c r="L46" s="4" t="s">
+      <c r="K46" s="12"/>
+      <c r="L46" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="M46" s="10"/>
-    </row>
-    <row r="47" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B47" s="10"/>
-      <c r="C47" s="10" t="s">
+      <c r="M46" s="12"/>
+    </row>
+    <row r="47" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="12"/>
+      <c r="C47" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10" t="s">
+      <c r="E47" s="12"/>
+      <c r="F47" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G47" s="10">
-        <v>1</v>
-      </c>
-      <c r="H47" s="10">
-        <v>1</v>
-      </c>
-      <c r="I47" s="11">
+      <c r="G47" s="13">
+        <v>1</v>
+      </c>
+      <c r="H47" s="13">
+        <v>1</v>
+      </c>
+      <c r="I47" s="14">
         <v>5</v>
       </c>
-      <c r="J47" s="11">
+      <c r="J47" s="14">
         <f>H47*I47</f>
         <v>5</v>
       </c>
-      <c r="K47" s="10"/>
-      <c r="L47" s="4" t="s">
+      <c r="K47" s="12"/>
+      <c r="L47" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="M47" s="10"/>
-    </row>
-    <row r="48" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B48" s="10"/>
-      <c r="C48" s="10" t="s">
+      <c r="M47" s="12"/>
+    </row>
+    <row r="48" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="12"/>
+      <c r="C48" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10" t="s">
+      <c r="E48" s="12"/>
+      <c r="F48" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G48" s="10">
+      <c r="G48" s="13">
         <v>20</v>
       </c>
-      <c r="H48" s="10">
-        <v>1</v>
-      </c>
-      <c r="I48" s="11">
+      <c r="H48" s="13">
+        <v>1</v>
+      </c>
+      <c r="I48" s="14">
         <v>8</v>
       </c>
-      <c r="J48" s="10">
+      <c r="J48" s="12">
         <f>H48*I48</f>
         <v>8</v>
       </c>
-      <c r="K48" s="10"/>
-      <c r="L48" s="4" t="s">
+      <c r="K48" s="12"/>
+      <c r="L48" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M48" s="10"/>
-    </row>
-    <row r="49" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="B49" s="10"/>
-      <c r="C49" s="10" t="s">
+      <c r="M48" s="12"/>
+    </row>
+    <row r="49" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B49" s="12"/>
+      <c r="C49" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="D49" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10" t="s">
+      <c r="E49" s="12"/>
+      <c r="F49" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="G49" s="10">
+      <c r="G49" s="13">
         <v>11</v>
       </c>
-      <c r="H49" s="10">
-        <v>1</v>
-      </c>
-      <c r="I49" s="11">
+      <c r="H49" s="13">
+        <v>1</v>
+      </c>
+      <c r="I49" s="14">
         <v>3</v>
       </c>
-      <c r="J49" s="10">
+      <c r="J49" s="12">
         <f>H49*I49</f>
         <v>3</v>
       </c>
-      <c r="K49" s="10"/>
-      <c r="L49" s="4" t="s">
+      <c r="K49" s="12"/>
+      <c r="L49" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="M49" s="10"/>
-    </row>
-    <row r="50" spans="1:13" s="12" customFormat="1">
-      <c r="A50" s="6"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="11"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="10"/>
-    </row>
-    <row r="51" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="A51" s="10" t="s">
+      <c r="M49" s="12"/>
+    </row>
+    <row r="50" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="12"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="12"/>
+    </row>
+    <row r="51" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="D51" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="F51" s="10" t="s">
+      <c r="F51" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="G51" s="10">
-        <v>1</v>
-      </c>
-      <c r="H51" s="10">
+      <c r="G51" s="13">
+        <v>1</v>
+      </c>
+      <c r="H51" s="13">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="I51" s="11">
+      <c r="I51" s="14">
         <v>4800</v>
       </c>
-      <c r="J51" s="10">
+      <c r="J51" s="12">
         <f>H51*I51</f>
         <v>196.8</v>
       </c>
-      <c r="K51" s="10"/>
-      <c r="L51" s="4" t="s">
+      <c r="K51" s="12"/>
+      <c r="L51" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="M51" s="10"/>
-    </row>
-    <row r="52" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="A52" s="10"/>
-      <c r="C52" s="10" t="s">
+      <c r="M51" s="12"/>
+    </row>
+    <row r="52" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="12"/>
+      <c r="C52" s="12" t="s">
         <v>146</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10" t="s">
+      <c r="E52" s="12"/>
+      <c r="F52" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="G52" s="10">
-        <v>1</v>
-      </c>
-      <c r="H52" s="10">
-        <v>1</v>
-      </c>
-      <c r="I52" s="10">
+      <c r="G52" s="13">
+        <v>1</v>
+      </c>
+      <c r="H52" s="13">
+        <v>1</v>
+      </c>
+      <c r="I52" s="13">
         <v>429</v>
       </c>
-      <c r="J52" s="10">
+      <c r="J52" s="12">
         <f>H52*I52</f>
         <v>429</v>
       </c>
-      <c r="K52" s="10"/>
-      <c r="L52" s="4" t="s">
+      <c r="K52" s="12"/>
+      <c r="L52" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="M52" s="10"/>
-    </row>
-    <row r="53" spans="1:13" s="12" customFormat="1">
-      <c r="A53" s="10"/>
-      <c r="C53" s="10" t="s">
+      <c r="M52" s="12"/>
+    </row>
+    <row r="53" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="12"/>
+      <c r="C53" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="F53" s="10" t="s">
+      <c r="F53" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="G53" s="10">
-        <v>1</v>
-      </c>
-      <c r="H53" s="10">
+      <c r="G53" s="13">
+        <v>1</v>
+      </c>
+      <c r="H53" s="13">
         <v>0.5</v>
       </c>
-      <c r="I53" s="11">
+      <c r="I53" s="14">
         <v>2299</v>
       </c>
-      <c r="J53" s="10">
+      <c r="J53" s="12">
         <f>H53*I53</f>
         <v>1149.5</v>
       </c>
-      <c r="K53" s="10"/>
-      <c r="L53" s="4" t="s">
+      <c r="K53" s="12"/>
+      <c r="L53" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="M53" s="10"/>
-    </row>
-    <row r="54" spans="1:13" s="6" customFormat="1" ht="14">
-      <c r="A54" s="10" t="s">
+      <c r="M53" s="12"/>
+    </row>
+    <row r="54" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10">
-        <v>1</v>
-      </c>
-      <c r="H54" s="10">
-        <v>1</v>
-      </c>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="10"/>
-    </row>
-    <row r="55" spans="1:13">
-      <c r="L55" s="4"/>
-    </row>
-    <row r="56" spans="1:13" s="12" customFormat="1">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="F56" s="14"/>
-      <c r="I56" s="15"/>
-      <c r="M56" s="6"/>
-    </row>
-    <row r="58" spans="1:13">
-      <c r="A58" s="6" t="s">
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="13">
+        <v>1</v>
+      </c>
+      <c r="H54" s="13">
+        <v>1</v>
+      </c>
+      <c r="I54" s="13"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="12"/>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="1:13" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="7"/>
+      <c r="B56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="19"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="20"/>
+      <c r="M56" s="7"/>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A58" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="B58" s="16" t="s">
+      <c r="B58" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="10" t="s">
         <v>155</v>
       </c>
       <c r="D58" t="s">
         <v>156</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="I58" s="13">
+      <c r="I58" s="17">
         <v>947</v>
       </c>
-      <c r="L58" s="8" t="s">
+      <c r="L58" s="10" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
-      <c r="B59" s="17"/>
-      <c r="C59" s="18" t="s">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B59" s="22"/>
+      <c r="C59" s="23" t="s">
         <v>159</v>
       </c>
       <c r="D59" t="s">
         <v>160</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="I59" s="13">
+      <c r="I59" s="17">
         <v>253</v>
       </c>
-      <c r="L59" s="8" t="s">
+      <c r="L59" s="10" t="s">
         <v>162</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="L8" display="https://www.amazon.co.jp/Arduino-Rev3-ATmega328-%E3%83%9E%E3%82%A4%E3%82%B3%E3%83%B3%E3%83%9C%E3%83%BC%E3%83%89-A000066/dp/B008GRTSV6/ref=sr_1_6?__mk_ja_JP=%E3%82%AB%E3%82%BF%E3%82%AB%E3%83%8A&amp;dchild=1&amp;keywords=%E3%82%A2%E3%83%AB%E3%83%87%E3%82%A3%E3%83%B" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="L33" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="L41" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="L30" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="L8" display="https://www.amazon.co.jp/Arduino-Rev3-ATmega328-%E3%83%9E%E3%82%A4%E3%82%B3%E3%83%B3%E3%83%9C%E3%83%BC%E3%83%89-A000066/dp/B008GRTSV6/ref=sr_1_6?__mk_ja_JP=%E3%82%AB%E3%82%BF%E3%82%AB%E3%83%8A&amp;dchild=1&amp;keywords=%E3%82%A2%E3%83%AB%E3%83%87%E3%82%A3%E3%83%B"/>
+    <hyperlink ref="L33" r:id="rId1"/>
+    <hyperlink ref="L41" r:id="rId2"/>
+    <hyperlink ref="L30" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
@@ -3341,15 +3351,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.08203125" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="5" customFormat="1" ht="48" customHeight="1">
+    <row r="1" spans="1:13" s="30" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3365,130 +3375,142 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4"/>
+      <c r="L1" s="5"/>
       <c r="M1" s="2"/>
     </row>
-    <row r="2" spans="1:13" ht="15.5">
-      <c r="I2" s="13"/>
-    </row>
-    <row r="4" spans="1:13" ht="15.5">
-      <c r="A4" s="20" t="s">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="D4" s="25"/>
+      <c r="E4" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" s="29">
+        <v>1</v>
+      </c>
+      <c r="G4" s="29">
+        <v>1</v>
+      </c>
+      <c r="H4" s="28">
+        <v>216.17</v>
+      </c>
+      <c r="I4" s="26">
+        <v>216.17</v>
+      </c>
+      <c r="J4" s="25"/>
+      <c r="K4" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="L4" s="25"/>
+    </row>
+    <row r="5" spans="1:13" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="25"/>
+      <c r="B5" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F4" s="8">
-        <v>1</v>
-      </c>
-      <c r="G4" s="8">
-        <v>1</v>
-      </c>
-      <c r="H4" s="13">
+      <c r="C5" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5" s="29">
+        <v>1</v>
+      </c>
+      <c r="G5" s="29">
+        <v>1</v>
+      </c>
+      <c r="H5" s="28">
+        <v>305</v>
+      </c>
+      <c r="I5" s="26">
         <v>216.17</v>
       </c>
-      <c r="I4" s="8">
-        <v>216.17</v>
-      </c>
-      <c r="K4" s="19" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="8" customFormat="1" ht="15.5">
-      <c r="A5"/>
-      <c r="B5" s="8" t="s">
+      <c r="K5" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="C5" t="s">
-        <v>184</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="F5" s="8">
-        <v>1</v>
-      </c>
-      <c r="G5" s="8">
-        <v>1</v>
-      </c>
-      <c r="H5" s="13">
-        <v>305</v>
-      </c>
-      <c r="I5" s="8">
-        <v>216.17</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="L5"/>
-    </row>
-    <row r="6" spans="1:13" s="8" customFormat="1" ht="15.5">
+      <c r="L5" s="25"/>
+    </row>
+    <row r="6" spans="1:13" s="10" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6"/>
-      <c r="D6" s="10"/>
+      <c r="D6" s="12"/>
+      <c r="G6" s="16"/>
       <c r="H6"/>
-      <c r="I6" s="13"/>
+      <c r="I6" s="17"/>
       <c r="J6"/>
       <c r="M6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
-  <hyperlinks>
-    <hyperlink ref="K4" r:id="rId1" xr:uid="{5403D520-740C-4738-A8F5-6BD542DD9110}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:B6"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:2">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="2:2">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="2:2">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="2:2">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="2:2">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>178</v>
       </c>
